--- a/data/Planes de acción - TFG v2.xlsx
+++ b/data/Planes de acción - TFG v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://advisoryexpertsspain-my.sharepoint.com/personal/carlos_gonzalez_advisoryexperts_es/Documents/Proyectos/TFG/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{3F8BF34D-D80D-5744-862C-62ABFCC90973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D41FD4D-6251-4552-8BAB-D57FC2321A16}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{3F8BF34D-D80D-5744-862C-62ABFCC90973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F485624-1B3D-4C67-8877-C690AFE16A5D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Necesidades" sheetId="3" r:id="rId1"/>
@@ -38,13 +38,14 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="Filtro 3" guid="{8745C551-62D5-4240-A53F-D92EC92BD889}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 2" guid="{B691C057-3106-4870-AE17-3EF2FBAC0114}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 1" guid="{0D9E2468-7FAF-4BD0-AC36-C2E3170321A1}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 6" guid="{DFB89FC0-5343-4D31-AE56-18CDD52AEABA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Filtro 5" guid="{BEE8F531-F084-4F3F-80A7-3E2E4FC113C0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Filtro 4" guid="{D5D76285-A10F-44AE-9765-25F9167232C9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 5" guid="{BEE8F531-F084-4F3F-80A7-3E2E4FC113C0}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 6" guid="{DFB89FC0-5343-4D31-AE56-18CDD52AEABA}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 1" guid="{0D9E2468-7FAF-4BD0-AC36-C2E3170321A1}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 2" guid="{B691C057-3106-4870-AE17-3EF2FBAC0114}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Filtro 3" guid="{8745C551-62D5-4240-A53F-D92EC92BD889}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -3319,10 +3320,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{40118FB7-0A3A-4C9F-A454-19CAD7B07CE1}" name="ObjetosSociales" displayName="ObjetosSociales" ref="A1:B64" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:B64" xr:uid="{40118FB7-0A3A-4C9F-A454-19CAD7B07CE1}"/>
@@ -3535,7 +3532,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:CC1016"/>
+  <dimension ref="A1:F1016"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -12409,21 +12406,21 @@
   </sheetData>
   <autoFilter ref="A1:F1016" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <customSheetViews>
-    <customSheetView guid="{0D9E2468-7FAF-4BD0-AC36-C2E3170321A1}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{8745C551-62D5-4240-A53F-D92EC92BD889}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:O76" xr:uid="{487CAD74-9684-4D9A-9EBD-61DD5D877867}"/>
+      <autoFilter ref="A1:O76" xr:uid="{A8896FF2-64AF-4BC8-BF05-C530EB903914}"/>
+    </customSheetView>
+    <customSheetView guid="{B691C057-3106-4870-AE17-3EF2FBAC0114}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="A1:O76" xr:uid="{A37722A8-7636-4748-BB9F-1F1EDFE636F8}"/>
     </customSheetView>
     <customSheetView guid="{D5D76285-A10F-44AE-9765-25F9167232C9}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:O76" xr:uid="{506D1DBA-90CC-48A6-963D-B34D6A1C3D0E}"/>
+      <autoFilter ref="A1:O76" xr:uid="{29252ACC-94CD-48B4-85C5-BADBB4225B5C}"/>
     </customSheetView>
-    <customSheetView guid="{B691C057-3106-4870-AE17-3EF2FBAC0114}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{0D9E2468-7FAF-4BD0-AC36-C2E3170321A1}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:O76" xr:uid="{68A16E07-D201-45E2-B7F9-89191FD3E293}"/>
-    </customSheetView>
-    <customSheetView guid="{8745C551-62D5-4240-A53F-D92EC92BD889}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:O76" xr:uid="{4EBE7060-A512-478F-A322-DFCDE4047E09}"/>
+      <autoFilter ref="A1:O76" xr:uid="{3230208E-79A6-4A86-9EA6-824AD746B2C9}"/>
     </customSheetView>
   </customSheetViews>
   <dataValidations count="2">
@@ -26249,29 +26246,29 @@
   </sheetData>
   <autoFilter ref="A1:H205" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <customSheetViews>
-    <customSheetView guid="{B691C057-3106-4870-AE17-3EF2FBAC0114}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{BEE8F531-F084-4F3F-80A7-3E2E4FC113C0}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:R195" xr:uid="{CC5CC382-E552-4393-857B-576182FF7322}"/>
+      <autoFilter ref="B1:R241" xr:uid="{56F4FACB-5534-4C36-89D1-442255C4FEA8}"/>
+    </customSheetView>
+    <customSheetView guid="{D5D76285-A10F-44AE-9765-25F9167232C9}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="B1:R241" xr:uid="{D6F887E5-F2A4-4364-B296-B837D9216CE8}"/>
+    </customSheetView>
+    <customSheetView guid="{DFB89FC0-5343-4D31-AE56-18CDD52AEABA}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="B1:R241" xr:uid="{B3B84413-F8FC-4587-8BC6-26C8D8C2D454}"/>
+    </customSheetView>
+    <customSheetView guid="{8745C551-62D5-4240-A53F-D92EC92BD889}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="B1:R241" xr:uid="{AD74EA69-9493-4BE8-BBFE-15BEF9DCEFBA}"/>
     </customSheetView>
     <customSheetView guid="{0D9E2468-7FAF-4BD0-AC36-C2E3170321A1}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:R176" xr:uid="{D5F8E5C7-1CD3-45EB-9DFF-4BF45C61579B}"/>
+      <autoFilter ref="A1:R176" xr:uid="{1D687497-2E06-4540-B909-515F006B9054}"/>
     </customSheetView>
-    <customSheetView guid="{8745C551-62D5-4240-A53F-D92EC92BD889}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{B691C057-3106-4870-AE17-3EF2FBAC0114}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="B1:R241" xr:uid="{B34612CF-AAAB-4330-8194-5688170DE076}"/>
-    </customSheetView>
-    <customSheetView guid="{DFB89FC0-5343-4D31-AE56-18CDD52AEABA}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="B1:R241" xr:uid="{FE60339B-95C0-4B6F-B154-734755132A9F}"/>
-    </customSheetView>
-    <customSheetView guid="{D5D76285-A10F-44AE-9765-25F9167232C9}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="B1:R241" xr:uid="{22261ECE-A11D-452B-B3F0-859CDDF3833F}"/>
-    </customSheetView>
-    <customSheetView guid="{BEE8F531-F084-4F3F-80A7-3E2E4FC113C0}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="B1:R241" xr:uid="{D015A420-C955-4F5F-80B6-5B44090ED1AB}"/>
+      <autoFilter ref="A1:R195" xr:uid="{EA1E2B6A-EC6E-4131-9826-E54C484D0F61}"/>
     </customSheetView>
   </customSheetViews>
   <dataValidations disablePrompts="1" count="2">
@@ -26288,6 +26285,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C6ABB9E-6A8B-E24D-88D0-7BE911A40F07}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F564"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -26317,7 +26315,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>101011</v>
       </c>
@@ -26334,7 +26332,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>101011</v>
       </c>
@@ -26351,7 +26349,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>101011</v>
       </c>
@@ -26371,7 +26369,7 @@
         <v>45373</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>101011</v>
       </c>
@@ -26391,7 +26389,7 @@
         <v>45426</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>101011</v>
       </c>
@@ -26411,7 +26409,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>101011</v>
       </c>
@@ -26428,7 +26426,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>101011</v>
       </c>
@@ -26445,7 +26443,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>101011</v>
       </c>
@@ -26462,7 +26460,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>101011</v>
       </c>
@@ -26482,7 +26480,7 @@
         <v>45426</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>101011</v>
       </c>
@@ -26502,7 +26500,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>101011</v>
       </c>
@@ -26522,7 +26520,7 @@
         <v>45528</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>101011</v>
       </c>
@@ -26539,7 +26537,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>101011</v>
       </c>
@@ -26556,7 +26554,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>101011</v>
       </c>
@@ -26576,7 +26574,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>101011</v>
       </c>
@@ -26593,7 +26591,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>101011</v>
       </c>
@@ -26610,7 +26608,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>101011</v>
       </c>
@@ -26630,7 +26628,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>101011</v>
       </c>
@@ -26650,7 +26648,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>101011</v>
       </c>
@@ -26670,7 +26668,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>101011</v>
       </c>
@@ -26690,7 +26688,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>101011</v>
       </c>
@@ -26710,7 +26708,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>101011</v>
       </c>
@@ -26730,7 +26728,7 @@
         <v>45373</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>101011</v>
       </c>
@@ -26750,7 +26748,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>101011</v>
       </c>
@@ -26770,7 +26768,7 @@
         <v>45426</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>101011</v>
       </c>
@@ -26790,7 +26788,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>101011</v>
       </c>
@@ -26810,7 +26808,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>101011</v>
       </c>
@@ -26830,7 +26828,7 @@
         <v>45426</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>101011</v>
       </c>
@@ -26847,7 +26845,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>101011</v>
       </c>
@@ -26864,7 +26862,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>101011</v>
       </c>
@@ -26884,7 +26882,7 @@
         <v>45426</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>101011</v>
       </c>
@@ -26904,7 +26902,7 @@
         <v>45426</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>101011</v>
       </c>
@@ -26924,7 +26922,7 @@
         <v>45426</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>101011</v>
       </c>
@@ -26941,7 +26939,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>101011</v>
       </c>
@@ -26958,7 +26956,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>101011</v>
       </c>
@@ -26975,7 +26973,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>101011</v>
       </c>
@@ -26995,7 +26993,7 @@
         <v>45426</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>101011</v>
       </c>
@@ -27012,7 +27010,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>101012</v>
       </c>
@@ -27032,7 +27030,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>101012</v>
       </c>
@@ -27052,7 +27050,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>101012</v>
       </c>
@@ -27072,7 +27070,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>101012</v>
       </c>
@@ -27092,7 +27090,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>101012</v>
       </c>
@@ -27112,7 +27110,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>101012</v>
       </c>
@@ -27132,7 +27130,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>101012</v>
       </c>
@@ -27152,7 +27150,7 @@
         <v>45356</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>101012</v>
       </c>
@@ -27172,7 +27170,7 @@
         <v>45426</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>101012</v>
       </c>
@@ -27192,7 +27190,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>101012</v>
       </c>
@@ -27212,7 +27210,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>101012</v>
       </c>
@@ -27232,7 +27230,7 @@
         <v>45426</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>101012</v>
       </c>
@@ -27252,7 +27250,7 @@
         <v>45372</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>101014</v>
       </c>
@@ -27269,7 +27267,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>101018</v>
       </c>
@@ -27286,7 +27284,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>101019</v>
       </c>
@@ -27306,7 +27304,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>101019</v>
       </c>
@@ -27326,7 +27324,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>101019</v>
       </c>
@@ -27346,7 +27344,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>101019</v>
       </c>
@@ -27366,7 +27364,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>101019</v>
       </c>
@@ -27386,7 +27384,7 @@
         <v>45505</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>101019</v>
       </c>
@@ -27406,7 +27404,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>101019</v>
       </c>
@@ -27426,7 +27424,7 @@
         <v>45693</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>101019</v>
       </c>
@@ -27446,7 +27444,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>101019</v>
       </c>
@@ -27466,7 +27464,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>101019</v>
       </c>
@@ -27486,7 +27484,7 @@
         <v>45513</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>101019</v>
       </c>
@@ -27506,7 +27504,7 @@
         <v>45513</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>101019</v>
       </c>
@@ -27526,7 +27524,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>101019</v>
       </c>
@@ -27546,7 +27544,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>101019</v>
       </c>
@@ -27566,7 +27564,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>101020</v>
       </c>
@@ -27586,7 +27584,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>101020</v>
       </c>
@@ -27606,7 +27604,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>101020</v>
       </c>
@@ -27626,7 +27624,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>101020</v>
       </c>
@@ -27646,7 +27644,7 @@
         <v>45365</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>101020</v>
       </c>
@@ -27666,7 +27664,7 @@
         <v>45365</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>101020</v>
       </c>
@@ -27686,7 +27684,7 @@
         <v>45365</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>101020</v>
       </c>
@@ -27706,7 +27704,7 @@
         <v>45365</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>101020</v>
       </c>
@@ -27726,7 +27724,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>101020</v>
       </c>
@@ -27746,7 +27744,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>101020</v>
       </c>
@@ -27766,7 +27764,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>101020</v>
       </c>
@@ -27786,7 +27784,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>101020</v>
       </c>
@@ -27806,7 +27804,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>101020</v>
       </c>
@@ -27826,7 +27824,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>101020</v>
       </c>
@@ -27843,7 +27841,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>101020</v>
       </c>
@@ -27860,7 +27858,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>101020</v>
       </c>
@@ -27877,7 +27875,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>101020</v>
       </c>
@@ -27897,7 +27895,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>101020</v>
       </c>
@@ -27917,7 +27915,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>101020</v>
       </c>
@@ -27937,7 +27935,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>101020</v>
       </c>
@@ -27957,7 +27955,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>101020</v>
       </c>
@@ -27977,7 +27975,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>101020</v>
       </c>
@@ -27997,7 +27995,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>101020</v>
       </c>
@@ -28017,7 +28015,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>101020</v>
       </c>
@@ -28037,7 +28035,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>101020</v>
       </c>
@@ -28057,7 +28055,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>101020</v>
       </c>
@@ -28077,7 +28075,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>101020</v>
       </c>
@@ -28097,7 +28095,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>101044</v>
       </c>
@@ -28114,7 +28112,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>101696</v>
       </c>
@@ -28131,7 +28129,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>101696</v>
       </c>
@@ -28148,7 +28146,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>101696</v>
       </c>
@@ -28165,7 +28163,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>101696</v>
       </c>
@@ -28182,7 +28180,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>101696</v>
       </c>
@@ -28202,7 +28200,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>101696</v>
       </c>
@@ -28222,7 +28220,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>101696</v>
       </c>
@@ -28239,7 +28237,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101696</v>
       </c>
@@ -28256,7 +28254,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>101696</v>
       </c>
@@ -28273,7 +28271,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>101696</v>
       </c>
@@ -28293,7 +28291,7 @@
         <v>45436</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>101696</v>
       </c>
@@ -28313,7 +28311,7 @@
         <v>45426</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>101696</v>
       </c>
@@ -28330,7 +28328,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>101696</v>
       </c>
@@ -28350,7 +28348,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>101696</v>
       </c>
@@ -28367,7 +28365,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>101696</v>
       </c>
@@ -28384,7 +28382,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>101696</v>
       </c>
@@ -28401,7 +28399,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>101696</v>
       </c>
@@ -28418,7 +28416,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>101696</v>
       </c>
@@ -28435,7 +28433,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>101696</v>
       </c>
@@ -28452,7 +28450,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>101696</v>
       </c>
@@ -28469,7 +28467,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>101696</v>
       </c>
@@ -28486,7 +28484,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>101696</v>
       </c>
@@ -28503,7 +28501,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>101696</v>
       </c>
@@ -28523,7 +28521,7 @@
         <v>45426</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>101696</v>
       </c>
@@ -28540,7 +28538,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>101696</v>
       </c>
@@ -28557,7 +28555,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>101696</v>
       </c>
@@ -28574,7 +28572,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>101696</v>
       </c>
@@ -28591,7 +28589,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>101697</v>
       </c>
@@ -28611,7 +28609,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>101697</v>
       </c>
@@ -28631,7 +28629,7 @@
         <v>45554</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>101697</v>
       </c>
@@ -28651,7 +28649,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>101697</v>
       </c>
@@ -28671,7 +28669,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>101697</v>
       </c>
@@ -28691,7 +28689,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>101697</v>
       </c>
@@ -28711,7 +28709,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>101697</v>
       </c>
@@ -28728,7 +28726,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>101697</v>
       </c>
@@ -28748,7 +28746,7 @@
         <v>45245</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>101697</v>
       </c>
@@ -28768,7 +28766,7 @@
         <v>45372</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>101697</v>
       </c>
@@ -28788,7 +28786,7 @@
         <v>45412</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>101697</v>
       </c>
@@ -28808,7 +28806,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>101697</v>
       </c>
@@ -28828,7 +28826,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>101697</v>
       </c>
@@ -28848,7 +28846,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="135" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>101697</v>
       </c>
@@ -28865,7 +28863,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>101697</v>
       </c>
@@ -28885,7 +28883,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>101697</v>
       </c>
@@ -28905,7 +28903,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>101697</v>
       </c>
@@ -28925,7 +28923,7 @@
         <v>45554</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>101697</v>
       </c>
@@ -28945,7 +28943,7 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>101697</v>
       </c>
@@ -28962,7 +28960,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>101735</v>
       </c>
@@ -28979,7 +28977,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>101735</v>
       </c>
@@ -28996,7 +28994,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>101735</v>
       </c>
@@ -29013,7 +29011,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>101735</v>
       </c>
@@ -29030,7 +29028,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>101735</v>
       </c>
@@ -29047,7 +29045,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="146" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>101751</v>
       </c>
@@ -29067,7 +29065,7 @@
         <v>45358</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>101751</v>
       </c>
@@ -29087,7 +29085,7 @@
         <v>45378</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>101751</v>
       </c>
@@ -29107,7 +29105,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>101751</v>
       </c>
@@ -29127,7 +29125,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>101751</v>
       </c>
@@ -29147,7 +29145,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>101751</v>
       </c>
@@ -29167,7 +29165,7 @@
         <v>45358</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>101751</v>
       </c>
@@ -29187,7 +29185,7 @@
         <v>45358</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>101751</v>
       </c>
@@ -29207,7 +29205,7 @@
         <v>45358</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>101751</v>
       </c>
@@ -29227,7 +29225,7 @@
         <v>45358</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>101751</v>
       </c>
@@ -29247,7 +29245,7 @@
         <v>45358</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>101917</v>
       </c>
@@ -29267,7 +29265,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>101917</v>
       </c>
@@ -29287,7 +29285,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>101917</v>
       </c>
@@ -29307,7 +29305,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>101917</v>
       </c>
@@ -29327,7 +29325,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>101917</v>
       </c>
@@ -29347,7 +29345,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>101917</v>
       </c>
@@ -29367,7 +29365,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="162" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>101917</v>
       </c>
@@ -29387,7 +29385,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>101917</v>
       </c>
@@ -29407,7 +29405,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>101917</v>
       </c>
@@ -29427,7 +29425,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>101917</v>
       </c>
@@ -29447,7 +29445,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>101917</v>
       </c>
@@ -29467,7 +29465,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>101917</v>
       </c>
@@ -29487,7 +29485,7 @@
         <v>45513</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>101917</v>
       </c>
@@ -29507,7 +29505,7 @@
         <v>45693</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>101917</v>
       </c>
@@ -29527,7 +29525,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="170" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>101917</v>
       </c>
@@ -29547,7 +29545,7 @@
         <v>45505</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>101917</v>
       </c>
@@ -29567,7 +29565,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>101917</v>
       </c>
@@ -29587,7 +29585,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>101917</v>
       </c>
@@ -29607,7 +29605,7 @@
         <v>45513</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>101917</v>
       </c>
@@ -29627,7 +29625,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>101949</v>
       </c>
@@ -29647,7 +29645,7 @@
         <v>45392</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>101949</v>
       </c>
@@ -29667,7 +29665,7 @@
         <v>45362</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>101949</v>
       </c>
@@ -29684,7 +29682,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>101949</v>
       </c>
@@ -29704,7 +29702,7 @@
         <v>45362</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>101949</v>
       </c>
@@ -29724,7 +29722,7 @@
         <v>45362</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>101949</v>
       </c>
@@ -29744,7 +29742,7 @@
         <v>45362</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>101949</v>
       </c>
@@ -29764,7 +29762,7 @@
         <v>45362</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>101949</v>
       </c>
@@ -29784,7 +29782,7 @@
         <v>45362</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>101949</v>
       </c>
@@ -29801,7 +29799,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>101949</v>
       </c>
@@ -29818,7 +29816,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>101949</v>
       </c>
@@ -29835,7 +29833,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>101949</v>
       </c>
@@ -29855,7 +29853,7 @@
         <v>45362</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>101949</v>
       </c>
@@ -29875,7 +29873,7 @@
         <v>45362</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>101949</v>
       </c>
@@ -29895,7 +29893,7 @@
         <v>45362</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>101949</v>
       </c>
@@ -29915,7 +29913,7 @@
         <v>45392</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>101949</v>
       </c>
@@ -29935,7 +29933,7 @@
         <v>45392</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>101949</v>
       </c>
@@ -29955,7 +29953,7 @@
         <v>45392</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>101949</v>
       </c>
@@ -29975,7 +29973,7 @@
         <v>45392</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>101949</v>
       </c>
@@ -29995,7 +29993,7 @@
         <v>45392</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>101949</v>
       </c>
@@ -30015,7 +30013,7 @@
         <v>45392</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>101949</v>
       </c>
@@ -30035,7 +30033,7 @@
         <v>45392</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>101949</v>
       </c>
@@ -30055,7 +30053,7 @@
         <v>45362</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>102236</v>
       </c>
@@ -30075,7 +30073,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>102236</v>
       </c>
@@ -30095,7 +30093,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>102236</v>
       </c>
@@ -30115,7 +30113,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>102236</v>
       </c>
@@ -30135,7 +30133,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>102236</v>
       </c>
@@ -30155,7 +30153,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>102236</v>
       </c>
@@ -30175,7 +30173,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>102236</v>
       </c>
@@ -30195,7 +30193,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>102236</v>
       </c>
@@ -30215,7 +30213,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="205" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>102236</v>
       </c>
@@ -30235,7 +30233,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>102236</v>
       </c>
@@ -30255,7 +30253,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="207" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>102236</v>
       </c>
@@ -30275,7 +30273,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>102236</v>
       </c>
@@ -30295,7 +30293,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>102236</v>
       </c>
@@ -30315,7 +30313,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>102236</v>
       </c>
@@ -30335,7 +30333,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>102236</v>
       </c>
@@ -30355,7 +30353,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>102236</v>
       </c>
@@ -30375,7 +30373,7 @@
         <v>45390</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>102236</v>
       </c>
@@ -30392,7 +30390,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="214" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>102236</v>
       </c>
@@ -30409,7 +30407,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>102236</v>
       </c>
@@ -30426,7 +30424,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>102236</v>
       </c>
@@ -30439,7 +30437,7 @@
       <c r="D216" s="37"/>
       <c r="E216" s="82"/>
     </row>
-    <row r="217" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>102238</v>
       </c>
@@ -30459,7 +30457,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>102238</v>
       </c>
@@ -30479,7 +30477,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>102238</v>
       </c>
@@ -30499,7 +30497,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>102238</v>
       </c>
@@ -30519,7 +30517,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>102238</v>
       </c>
@@ -30539,7 +30537,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="222" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>102238</v>
       </c>
@@ -30559,7 +30557,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="223" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>102238</v>
       </c>
@@ -30579,7 +30577,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="224" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>102238</v>
       </c>
@@ -30599,7 +30597,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="225" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>102238</v>
       </c>
@@ -30619,7 +30617,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="226" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>102238</v>
       </c>
@@ -30639,7 +30637,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>102238</v>
       </c>
@@ -30659,7 +30657,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="228" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>102238</v>
       </c>
@@ -30679,7 +30677,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="229" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>102238</v>
       </c>
@@ -30699,7 +30697,7 @@
         <v>45357</v>
       </c>
     </row>
-    <row r="230" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>102332</v>
       </c>
@@ -30719,7 +30717,7 @@
         <v>45447</v>
       </c>
     </row>
-    <row r="231" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>102332</v>
       </c>
@@ -30739,7 +30737,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="232" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>102332</v>
       </c>
@@ -30759,7 +30757,7 @@
         <v>45447</v>
       </c>
     </row>
-    <row r="233" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>102332</v>
       </c>
@@ -30779,7 +30777,7 @@
         <v>45447</v>
       </c>
     </row>
-    <row r="234" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>102332</v>
       </c>
@@ -30799,7 +30797,7 @@
         <v>45447</v>
       </c>
     </row>
-    <row r="235" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>102332</v>
       </c>
@@ -30819,7 +30817,7 @@
         <v>45447</v>
       </c>
     </row>
-    <row r="236" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>102332</v>
       </c>
@@ -30839,7 +30837,7 @@
         <v>45377</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>102332</v>
       </c>
@@ -30859,7 +30857,7 @@
         <v>45447</v>
       </c>
     </row>
-    <row r="238" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>102332</v>
       </c>
@@ -30879,7 +30877,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="239" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>102332</v>
       </c>
@@ -30899,7 +30897,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="240" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>102332</v>
       </c>
@@ -30919,7 +30917,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="241" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>102332</v>
       </c>
@@ -30939,7 +30937,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="242" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>102332</v>
       </c>
@@ -30959,7 +30957,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="243" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>102332</v>
       </c>
@@ -30979,7 +30977,7 @@
         <v>45377</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>102332</v>
       </c>
@@ -30999,7 +30997,7 @@
         <v>45377</v>
       </c>
     </row>
-    <row r="245" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>102332</v>
       </c>
@@ -31019,7 +31017,7 @@
         <v>45377</v>
       </c>
     </row>
-    <row r="246" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>102332</v>
       </c>
@@ -31039,7 +31037,7 @@
         <v>45377</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>102400</v>
       </c>
@@ -31059,7 +31057,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="248" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>102400</v>
       </c>
@@ -31079,7 +31077,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="249" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>102400</v>
       </c>
@@ -31099,7 +31097,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="250" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>102400</v>
       </c>
@@ -31119,7 +31117,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="251" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>102400</v>
       </c>
@@ -31139,7 +31137,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="252" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>102400</v>
       </c>
@@ -31159,7 +31157,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="253" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>102400</v>
       </c>
@@ -31179,7 +31177,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="254" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>102400</v>
       </c>
@@ -31199,7 +31197,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>102400</v>
       </c>
@@ -31219,7 +31217,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>102400</v>
       </c>
@@ -31239,7 +31237,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>102400</v>
       </c>
@@ -31259,7 +31257,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>102400</v>
       </c>
@@ -31279,7 +31277,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="259" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>102552</v>
       </c>
@@ -31299,7 +31297,7 @@
         <v>46008</v>
       </c>
     </row>
-    <row r="260" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>102552</v>
       </c>
@@ -31319,7 +31317,7 @@
         <v>45664</v>
       </c>
     </row>
-    <row r="261" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>102552</v>
       </c>
@@ -31339,7 +31337,7 @@
         <v>45637</v>
       </c>
     </row>
-    <row r="262" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>102552</v>
       </c>
@@ -31359,7 +31357,7 @@
         <v>45597</v>
       </c>
     </row>
-    <row r="263" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>102552</v>
       </c>
@@ -31379,7 +31377,7 @@
         <v>45637</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>103180</v>
       </c>
@@ -31399,7 +31397,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>103550</v>
       </c>
@@ -31419,7 +31417,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="266" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>103550</v>
       </c>
@@ -31439,7 +31437,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="267" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>103550</v>
       </c>
@@ -31459,7 +31457,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="268" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>103550</v>
       </c>
@@ -31479,7 +31477,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="269" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>103550</v>
       </c>
@@ -31499,7 +31497,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="270" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>103550</v>
       </c>
@@ -31519,7 +31517,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="271" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>103550</v>
       </c>
@@ -31539,7 +31537,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="272" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>103550</v>
       </c>
@@ -31559,7 +31557,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="273" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>103550</v>
       </c>
@@ -31579,7 +31577,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>103762</v>
       </c>
@@ -31599,7 +31597,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="275" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>103762</v>
       </c>
@@ -31619,7 +31617,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>103762</v>
       </c>
@@ -31639,7 +31637,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="277" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>103762</v>
       </c>
@@ -31659,7 +31657,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="278" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>103762</v>
       </c>
@@ -31679,7 +31677,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>103762</v>
       </c>
@@ -31699,7 +31697,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>103762</v>
       </c>
@@ -31719,7 +31717,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="281" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>103762</v>
       </c>
@@ -31739,7 +31737,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>103762</v>
       </c>
@@ -31759,7 +31757,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="283" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>103762</v>
       </c>
@@ -31779,7 +31777,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>103762</v>
       </c>
@@ -31799,7 +31797,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>103762</v>
       </c>
@@ -31819,7 +31817,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>103762</v>
       </c>
@@ -31839,7 +31837,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>103762</v>
       </c>
@@ -31859,7 +31857,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>103762</v>
       </c>
@@ -31879,7 +31877,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>104783</v>
       </c>
@@ -31899,7 +31897,7 @@
         <v>45977</v>
       </c>
     </row>
-    <row r="290" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>104783</v>
       </c>
@@ -31919,7 +31917,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>104783</v>
       </c>
@@ -31939,7 +31937,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="292" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>104783</v>
       </c>
@@ -31959,7 +31957,7 @@
         <v>45452</v>
       </c>
     </row>
-    <row r="293" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>104783</v>
       </c>
@@ -31979,7 +31977,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="294" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>104783</v>
       </c>
@@ -31999,7 +31997,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="295" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>104783</v>
       </c>
@@ -32019,7 +32017,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="296" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>104783</v>
       </c>
@@ -32039,7 +32037,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>104783</v>
       </c>
@@ -32059,7 +32057,7 @@
         <v>45446</v>
       </c>
     </row>
-    <row r="298" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>104783</v>
       </c>
@@ -32099,7 +32097,7 @@
         <v>45455</v>
       </c>
     </row>
-    <row r="300" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>105609</v>
       </c>
@@ -32119,7 +32117,7 @@
         <v>45469</v>
       </c>
     </row>
-    <row r="301" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>105609</v>
       </c>
@@ -32139,7 +32137,7 @@
         <v>45469</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>105609</v>
       </c>
@@ -32159,7 +32157,7 @@
         <v>45528</v>
       </c>
     </row>
-    <row r="303" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>105609</v>
       </c>
@@ -32179,7 +32177,7 @@
         <v>45469</v>
       </c>
     </row>
-    <row r="304" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>105609</v>
       </c>
@@ -32199,7 +32197,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="305" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>105609</v>
       </c>
@@ -32219,7 +32217,7 @@
         <v>45469</v>
       </c>
     </row>
-    <row r="306" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>105609</v>
       </c>
@@ -32239,7 +32237,7 @@
         <v>45469</v>
       </c>
     </row>
-    <row r="307" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>105609</v>
       </c>
@@ -32259,7 +32257,7 @@
         <v>45469</v>
       </c>
     </row>
-    <row r="308" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>105609</v>
       </c>
@@ -32279,7 +32277,7 @@
         <v>45454</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>105609</v>
       </c>
@@ -32299,7 +32297,7 @@
         <v>45454</v>
       </c>
     </row>
-    <row r="310" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>105609</v>
       </c>
@@ -32319,7 +32317,7 @@
         <v>45469</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>105611</v>
       </c>
@@ -32339,7 +32337,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>105611</v>
       </c>
@@ -32359,7 +32357,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>105611</v>
       </c>
@@ -32379,7 +32377,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="314" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>105611</v>
       </c>
@@ -32399,7 +32397,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="315" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>105611</v>
       </c>
@@ -32419,7 +32417,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="316" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>105611</v>
       </c>
@@ -32439,7 +32437,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>105611</v>
       </c>
@@ -32459,7 +32457,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="318" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>105611</v>
       </c>
@@ -32479,7 +32477,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>105611</v>
       </c>
@@ -32499,7 +32497,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="320" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>105611</v>
       </c>
@@ -32519,7 +32517,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="321" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>105611</v>
       </c>
@@ -32539,7 +32537,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="322" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>105611</v>
       </c>
@@ -32559,7 +32557,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="323" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>105611</v>
       </c>
@@ -32579,7 +32577,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>105611</v>
       </c>
@@ -32599,7 +32597,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>105611</v>
       </c>
@@ -32619,7 +32617,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>105611</v>
       </c>
@@ -32639,7 +32637,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>105611</v>
       </c>
@@ -32659,7 +32657,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>105611</v>
       </c>
@@ -32679,7 +32677,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>105611</v>
       </c>
@@ -32699,7 +32697,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="330" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>105611</v>
       </c>
@@ -32719,7 +32717,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="331" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>105611</v>
       </c>
@@ -32739,7 +32737,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="332" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>105611</v>
       </c>
@@ -32759,7 +32757,7 @@
         <v>45741</v>
       </c>
     </row>
-    <row r="333" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>105611</v>
       </c>
@@ -32779,7 +32777,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>105611</v>
       </c>
@@ -32799,7 +32797,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>105613</v>
       </c>
@@ -32819,7 +32817,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>105613</v>
       </c>
@@ -32839,7 +32837,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="337" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>105613</v>
       </c>
@@ -32859,7 +32857,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="338" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>105613</v>
       </c>
@@ -32879,7 +32877,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="339" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>105613</v>
       </c>
@@ -32899,7 +32897,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="340" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>105613</v>
       </c>
@@ -32919,7 +32917,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="341" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>105613</v>
       </c>
@@ -32939,7 +32937,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="342" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>105613</v>
       </c>
@@ -32959,7 +32957,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>105613</v>
       </c>
@@ -32979,7 +32977,7 @@
         <v>45477</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>105613</v>
       </c>
@@ -32999,7 +32997,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="345" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>105613</v>
       </c>
@@ -33019,7 +33017,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="346" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>105613</v>
       </c>
@@ -33039,7 +33037,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="347" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>105613</v>
       </c>
@@ -33059,7 +33057,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="348" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>105613</v>
       </c>
@@ -33079,7 +33077,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="349" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>105613</v>
       </c>
@@ -33099,7 +33097,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="350" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>105613</v>
       </c>
@@ -33119,7 +33117,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>105613</v>
       </c>
@@ -33139,7 +33137,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>105613</v>
       </c>
@@ -33159,7 +33157,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>105613</v>
       </c>
@@ -33179,7 +33177,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>105613</v>
       </c>
@@ -33199,7 +33197,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>105613</v>
       </c>
@@ -33219,7 +33217,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>105613</v>
       </c>
@@ -33239,7 +33237,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>105613</v>
       </c>
@@ -33259,7 +33257,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="358" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>105613</v>
       </c>
@@ -33279,7 +33277,7 @@
         <v>45462</v>
       </c>
     </row>
-    <row r="359" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>105613</v>
       </c>
@@ -33299,7 +33297,7 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="360" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>105613</v>
       </c>
@@ -33319,7 +33317,7 @@
         <v>45483</v>
       </c>
     </row>
-    <row r="361" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>105613</v>
       </c>
@@ -33339,7 +33337,7 @@
         <v>45483</v>
       </c>
     </row>
-    <row r="362" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>105613</v>
       </c>
@@ -33359,7 +33357,7 @@
         <v>45483</v>
       </c>
     </row>
-    <row r="363" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>105613</v>
       </c>
@@ -33379,7 +33377,7 @@
         <v>45483</v>
       </c>
     </row>
-    <row r="364" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>105613</v>
       </c>
@@ -33399,7 +33397,7 @@
         <v>45483</v>
       </c>
     </row>
-    <row r="365" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>105613</v>
       </c>
@@ -33419,7 +33417,7 @@
         <v>45477</v>
       </c>
     </row>
-    <row r="366" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>105613</v>
       </c>
@@ -33439,7 +33437,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="367" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>105613</v>
       </c>
@@ -33459,7 +33457,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="368" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>105613</v>
       </c>
@@ -33479,7 +33477,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="369" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>105613</v>
       </c>
@@ -33499,7 +33497,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="370" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>105613</v>
       </c>
@@ -33519,7 +33517,7 @@
         <v>45475</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>106062</v>
       </c>
@@ -33539,7 +33537,7 @@
         <v>45552</v>
       </c>
     </row>
-    <row r="372" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>106062</v>
       </c>
@@ -33559,7 +33557,7 @@
         <v>45552</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>106062</v>
       </c>
@@ -33579,7 +33577,7 @@
         <v>45552</v>
       </c>
     </row>
-    <row r="374" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>106062</v>
       </c>
@@ -33599,7 +33597,7 @@
         <v>45552</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>106062</v>
       </c>
@@ -33619,7 +33617,7 @@
         <v>45552</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>106062</v>
       </c>
@@ -33639,7 +33637,7 @@
         <v>45552</v>
       </c>
     </row>
-    <row r="377" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>106064</v>
       </c>
@@ -33659,7 +33657,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="378" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>106064</v>
       </c>
@@ -33679,7 +33677,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="379" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>106064</v>
       </c>
@@ -33699,7 +33697,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="380" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>106064</v>
       </c>
@@ -33719,7 +33717,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="381" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>106064</v>
       </c>
@@ -33739,7 +33737,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="382" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>106064</v>
       </c>
@@ -33759,7 +33757,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="383" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>106064</v>
       </c>
@@ -33779,7 +33777,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="384" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>106064</v>
       </c>
@@ -33799,7 +33797,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="385" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>106064</v>
       </c>
@@ -33819,7 +33817,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="386" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>106064</v>
       </c>
@@ -33839,7 +33837,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="387" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>106065</v>
       </c>
@@ -33859,7 +33857,7 @@
         <v>45652</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>106065</v>
       </c>
@@ -33879,7 +33877,7 @@
         <v>45642</v>
       </c>
     </row>
-    <row r="389" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>106065</v>
       </c>
@@ -33899,7 +33897,7 @@
         <v>45642</v>
       </c>
     </row>
-    <row r="390" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>106065</v>
       </c>
@@ -33919,7 +33917,7 @@
         <v>45642</v>
       </c>
     </row>
-    <row r="391" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>106065</v>
       </c>
@@ -33939,7 +33937,7 @@
         <v>45642</v>
       </c>
     </row>
-    <row r="392" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>106065</v>
       </c>
@@ -33959,7 +33957,7 @@
         <v>45642</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>106065</v>
       </c>
@@ -33979,7 +33977,7 @@
         <v>45642</v>
       </c>
     </row>
-    <row r="394" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>106077</v>
       </c>
@@ -33999,7 +33997,7 @@
         <v>45514</v>
       </c>
     </row>
-    <row r="395" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>106077</v>
       </c>
@@ -34019,7 +34017,7 @@
         <v>45558</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>106077</v>
       </c>
@@ -34039,7 +34037,7 @@
         <v>45558</v>
       </c>
     </row>
-    <row r="397" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>106077</v>
       </c>
@@ -34059,7 +34057,7 @@
         <v>45514</v>
       </c>
     </row>
-    <row r="398" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>106077</v>
       </c>
@@ -34079,7 +34077,7 @@
         <v>45514</v>
       </c>
     </row>
-    <row r="399" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>106077</v>
       </c>
@@ -34099,7 +34097,7 @@
         <v>45514</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>106077</v>
       </c>
@@ -34119,7 +34117,7 @@
         <v>45514</v>
       </c>
     </row>
-    <row r="401" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>106700</v>
       </c>
@@ -34139,7 +34137,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="402" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>106700</v>
       </c>
@@ -34159,7 +34157,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="403" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>106700</v>
       </c>
@@ -34179,7 +34177,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>106700</v>
       </c>
@@ -34199,7 +34197,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>106700</v>
       </c>
@@ -34219,7 +34217,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>106700</v>
       </c>
@@ -34239,7 +34237,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>106700</v>
       </c>
@@ -34259,7 +34257,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="408" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>106700</v>
       </c>
@@ -34279,7 +34277,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="409" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>106700</v>
       </c>
@@ -34299,7 +34297,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="410" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>106700</v>
       </c>
@@ -34319,7 +34317,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>106700</v>
       </c>
@@ -34339,7 +34337,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>106700</v>
       </c>
@@ -34359,7 +34357,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="413" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>106700</v>
       </c>
@@ -34379,7 +34377,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="414" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>106700</v>
       </c>
@@ -34399,7 +34397,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="415" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>106700</v>
       </c>
@@ -34419,7 +34417,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="416" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>106700</v>
       </c>
@@ -34439,7 +34437,7 @@
         <v>45531</v>
       </c>
     </row>
-    <row r="417" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>106965</v>
       </c>
@@ -34459,7 +34457,7 @@
         <v>45518</v>
       </c>
     </row>
-    <row r="418" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>111551</v>
       </c>
@@ -34479,7 +34477,7 @@
         <v>45572</v>
       </c>
     </row>
-    <row r="419" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>111551</v>
       </c>
@@ -34499,7 +34497,7 @@
         <v>45572</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>111551</v>
       </c>
@@ -34519,7 +34517,7 @@
         <v>45572</v>
       </c>
     </row>
-    <row r="421" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>111551</v>
       </c>
@@ -34539,7 +34537,7 @@
         <v>45573</v>
       </c>
     </row>
-    <row r="422" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>111551</v>
       </c>
@@ -34559,7 +34557,7 @@
         <v>45572</v>
       </c>
     </row>
-    <row r="423" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>111551</v>
       </c>
@@ -34579,7 +34577,7 @@
         <v>45572</v>
       </c>
     </row>
-    <row r="424" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>111551</v>
       </c>
@@ -34599,7 +34597,7 @@
         <v>45572</v>
       </c>
     </row>
-    <row r="425" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>111551</v>
       </c>
@@ -34619,7 +34617,7 @@
         <v>45572</v>
       </c>
     </row>
-    <row r="426" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>111551</v>
       </c>
@@ -34639,7 +34637,7 @@
         <v>45572</v>
       </c>
     </row>
-    <row r="427" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>111551</v>
       </c>
@@ -34659,7 +34657,7 @@
         <v>45572</v>
       </c>
     </row>
-    <row r="428" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>111551</v>
       </c>
@@ -34679,7 +34677,7 @@
         <v>45572</v>
       </c>
     </row>
-    <row r="429" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>111865</v>
       </c>
@@ -34699,7 +34697,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="430" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>111865</v>
       </c>
@@ -34719,7 +34717,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="431" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>111865</v>
       </c>
@@ -34739,7 +34737,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="432" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>111865</v>
       </c>
@@ -34759,7 +34757,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="433" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>111865</v>
       </c>
@@ -34779,7 +34777,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="434" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>111865</v>
       </c>
@@ -34799,7 +34797,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="435" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>111865</v>
       </c>
@@ -34819,7 +34817,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="436" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>111865</v>
       </c>
@@ -34839,7 +34837,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="437" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>111865</v>
       </c>
@@ -34859,7 +34857,7 @@
         <v>45594</v>
       </c>
     </row>
-    <row r="438" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>111866</v>
       </c>
@@ -34879,7 +34877,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="439" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>111866</v>
       </c>
@@ -34899,7 +34897,7 @@
         <v>45607</v>
       </c>
     </row>
-    <row r="440" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>111866</v>
       </c>
@@ -34919,7 +34917,7 @@
         <v>45607</v>
       </c>
     </row>
-    <row r="441" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>111866</v>
       </c>
@@ -34939,7 +34937,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="442" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>111866</v>
       </c>
@@ -34959,7 +34957,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>111866</v>
       </c>
@@ -34979,7 +34977,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="444" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>111866</v>
       </c>
@@ -34999,7 +34997,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>111866</v>
       </c>
@@ -35019,7 +35017,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="446" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>111866</v>
       </c>
@@ -35039,7 +35037,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>111866</v>
       </c>
@@ -35059,7 +35057,7 @@
         <v>45607</v>
       </c>
     </row>
-    <row r="448" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>111866</v>
       </c>
@@ -35079,7 +35077,7 @@
         <v>45607</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>111866</v>
       </c>
@@ -35099,7 +35097,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="450" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>111866</v>
       </c>
@@ -35119,7 +35117,7 @@
         <v>45607</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>111866</v>
       </c>
@@ -35139,7 +35137,7 @@
         <v>45607</v>
       </c>
     </row>
-    <row r="452" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>114477</v>
       </c>
@@ -35159,7 +35157,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="453" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>114477</v>
       </c>
@@ -35179,7 +35177,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>114477</v>
       </c>
@@ -35199,7 +35197,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="455" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>114477</v>
       </c>
@@ -35219,7 +35217,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="456" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>114477</v>
       </c>
@@ -35239,7 +35237,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="457" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>114636</v>
       </c>
@@ -35259,7 +35257,7 @@
         <v>45610</v>
       </c>
     </row>
-    <row r="458" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>114636</v>
       </c>
@@ -35279,7 +35277,7 @@
         <v>45610</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>114636</v>
       </c>
@@ -35299,7 +35297,7 @@
         <v>45609</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>114637</v>
       </c>
@@ -35319,7 +35317,7 @@
         <v>45614</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>114637</v>
       </c>
@@ -35339,7 +35337,7 @@
         <v>45614</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>114637</v>
       </c>
@@ -35359,7 +35357,7 @@
         <v>45614</v>
       </c>
     </row>
-    <row r="463" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>114637</v>
       </c>
@@ -35379,7 +35377,7 @@
         <v>45614</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>114637</v>
       </c>
@@ -35399,7 +35397,7 @@
         <v>45614</v>
       </c>
     </row>
-    <row r="465" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>114637</v>
       </c>
@@ -35419,7 +35417,7 @@
         <v>45614</v>
       </c>
     </row>
-    <row r="466" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>114637</v>
       </c>
@@ -35439,7 +35437,7 @@
         <v>45614</v>
       </c>
     </row>
-    <row r="467" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>114723</v>
       </c>
@@ -35459,7 +35457,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="468" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>114723</v>
       </c>
@@ -35479,7 +35477,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="469" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>114723</v>
       </c>
@@ -35499,7 +35497,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="470" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>114723</v>
       </c>
@@ -35519,7 +35517,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="471" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>114723</v>
       </c>
@@ -35539,7 +35537,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>114723</v>
       </c>
@@ -35559,7 +35557,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="473" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>114723</v>
       </c>
@@ -35579,7 +35577,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>114724</v>
       </c>
@@ -35599,7 +35597,7 @@
         <v>45618</v>
       </c>
     </row>
-    <row r="475" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>114724</v>
       </c>
@@ -35619,7 +35617,7 @@
         <v>45618</v>
       </c>
     </row>
-    <row r="476" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>114724</v>
       </c>
@@ -35639,7 +35637,7 @@
         <v>45618</v>
       </c>
     </row>
-    <row r="477" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>114724</v>
       </c>
@@ -35659,7 +35657,7 @@
         <v>45618</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>114725</v>
       </c>
@@ -35679,7 +35677,7 @@
         <v>45932</v>
       </c>
     </row>
-    <row r="479" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>115848</v>
       </c>
@@ -35699,7 +35697,7 @@
         <v>45637</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>115848</v>
       </c>
@@ -35719,7 +35717,7 @@
         <v>45636</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>115848</v>
       </c>
@@ -35739,7 +35737,7 @@
         <v>45636</v>
       </c>
     </row>
-    <row r="482" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>115848</v>
       </c>
@@ -35759,7 +35757,7 @@
         <v>45636</v>
       </c>
     </row>
-    <row r="483" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>115854</v>
       </c>
@@ -35779,7 +35777,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="484" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>115854</v>
       </c>
@@ -35799,7 +35797,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>115854</v>
       </c>
@@ -35819,7 +35817,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="486" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>115854</v>
       </c>
@@ -35839,7 +35837,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="487" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>115854</v>
       </c>
@@ -35859,7 +35857,7 @@
         <v>45659</v>
       </c>
     </row>
-    <row r="488" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>116017</v>
       </c>
@@ -35879,7 +35877,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>116017</v>
       </c>
@@ -35899,7 +35897,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="490" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>116239</v>
       </c>
@@ -35919,7 +35917,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="491" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>116239</v>
       </c>
@@ -35939,7 +35937,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="492" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>116239</v>
       </c>
@@ -35959,7 +35957,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>116239</v>
       </c>
@@ -35979,7 +35977,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>116239</v>
       </c>
@@ -35999,7 +35997,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="495" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>116259</v>
       </c>
@@ -36019,7 +36017,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="496" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>116259</v>
       </c>
@@ -36039,7 +36037,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="497" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>116259</v>
       </c>
@@ -36059,7 +36057,7 @@
         <v>45704</v>
       </c>
     </row>
-    <row r="498" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>116371</v>
       </c>
@@ -36079,7 +36077,7 @@
         <v>45638</v>
       </c>
     </row>
-    <row r="499" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>116371</v>
       </c>
@@ -36099,7 +36097,7 @@
         <v>45645</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>117283</v>
       </c>
@@ -36119,7 +36117,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>117283</v>
       </c>
@@ -36139,7 +36137,7 @@
         <v>45687</v>
       </c>
     </row>
-    <row r="502" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>117283</v>
       </c>
@@ -36159,7 +36157,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>117662</v>
       </c>
@@ -36179,7 +36177,7 @@
         <v>45715</v>
       </c>
     </row>
-    <row r="504" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>117662</v>
       </c>
@@ -36199,7 +36197,7 @@
         <v>45715</v>
       </c>
     </row>
-    <row r="505" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>117662</v>
       </c>
@@ -36219,7 +36217,7 @@
         <v>45715</v>
       </c>
     </row>
-    <row r="506" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>117662</v>
       </c>
@@ -36239,7 +36237,7 @@
         <v>45715</v>
       </c>
     </row>
-    <row r="507" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>117662</v>
       </c>
@@ -36259,7 +36257,7 @@
         <v>45715</v>
       </c>
     </row>
-    <row r="508" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>117662</v>
       </c>
@@ -36279,7 +36277,7 @@
         <v>45715</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>117662</v>
       </c>
@@ -36299,7 +36297,7 @@
         <v>45715</v>
       </c>
     </row>
-    <row r="510" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>117662</v>
       </c>
@@ -36319,7 +36317,7 @@
         <v>45715</v>
       </c>
     </row>
-    <row r="511" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>117662</v>
       </c>
@@ -36339,7 +36337,7 @@
         <v>45715</v>
       </c>
     </row>
-    <row r="512" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>117662</v>
       </c>
@@ -36359,7 +36357,7 @@
         <v>45715</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>118008</v>
       </c>
@@ -36379,7 +36377,7 @@
         <v>45803</v>
       </c>
     </row>
-    <row r="514" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>118008</v>
       </c>
@@ -36399,7 +36397,7 @@
         <v>45803</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>118008</v>
       </c>
@@ -36419,7 +36417,7 @@
         <v>45803</v>
       </c>
     </row>
-    <row r="516" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>118219</v>
       </c>
@@ -36439,7 +36437,7 @@
         <v>45939</v>
       </c>
     </row>
-    <row r="517" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>118219</v>
       </c>
@@ -36459,7 +36457,7 @@
         <v>45939</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>118229</v>
       </c>
@@ -36479,7 +36477,7 @@
         <v>45692</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>119210</v>
       </c>
@@ -36499,7 +36497,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="520" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>119210</v>
       </c>
@@ -36519,7 +36517,7 @@
         <v>45896</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>119210</v>
       </c>
@@ -36539,7 +36537,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>119210</v>
       </c>
@@ -36559,7 +36557,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>119210</v>
       </c>
@@ -36579,7 +36577,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="524" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>119210</v>
       </c>
@@ -36599,7 +36597,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>119210</v>
       </c>
@@ -36619,7 +36617,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="526" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>119210</v>
       </c>
@@ -36639,7 +36637,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="527" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>119210</v>
       </c>
@@ -36659,7 +36657,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="528" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>119210</v>
       </c>
@@ -36679,7 +36677,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="529" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>121750</v>
       </c>
@@ -36699,7 +36697,7 @@
         <v>45745</v>
       </c>
     </row>
-    <row r="530" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>126771</v>
       </c>
@@ -36719,7 +36717,7 @@
         <v>45827</v>
       </c>
     </row>
-    <row r="531" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>126771</v>
       </c>
@@ -36739,7 +36737,7 @@
         <v>45827</v>
       </c>
     </row>
-    <row r="532" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>126771</v>
       </c>
@@ -36759,7 +36757,7 @@
         <v>45827</v>
       </c>
     </row>
-    <row r="533" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>126771</v>
       </c>
@@ -36779,7 +36777,7 @@
         <v>45827</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>126771</v>
       </c>
@@ -36799,7 +36797,7 @@
         <v>45827</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>128379</v>
       </c>
@@ -36819,7 +36817,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>128379</v>
       </c>
@@ -36839,7 +36837,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>128379</v>
       </c>
@@ -36859,7 +36857,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>128379</v>
       </c>
@@ -36879,7 +36877,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>128379</v>
       </c>
@@ -36899,7 +36897,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>128379</v>
       </c>
@@ -36919,7 +36917,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>128379</v>
       </c>
@@ -36939,7 +36937,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>128379</v>
       </c>
@@ -36959,7 +36957,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="543" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>140591</v>
       </c>
@@ -36979,7 +36977,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="544" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>144566</v>
       </c>
@@ -36999,7 +36997,7 @@
         <v>45505</v>
       </c>
     </row>
-    <row r="545" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>144566</v>
       </c>
@@ -37019,7 +37017,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="546" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>144566</v>
       </c>
@@ -37039,7 +37037,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="547" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>144566</v>
       </c>
@@ -37059,7 +37057,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="548" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>144566</v>
       </c>
@@ -37079,7 +37077,7 @@
         <v>45693</v>
       </c>
     </row>
-    <row r="549" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>144566</v>
       </c>
@@ -37099,7 +37097,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>144566</v>
       </c>
@@ -37119,7 +37117,7 @@
         <v>45513</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>144566</v>
       </c>
@@ -37139,7 +37137,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="552" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>144566</v>
       </c>
@@ -37159,7 +37157,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="553" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>144566</v>
       </c>
@@ -37179,7 +37177,7 @@
         <v>45386</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>144566</v>
       </c>
@@ -37199,7 +37197,7 @@
         <v>45513</v>
       </c>
     </row>
-    <row r="555" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>144566</v>
       </c>
@@ -37219,7 +37217,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="556" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>144566</v>
       </c>
@@ -37239,7 +37237,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="557" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>144566</v>
       </c>
@@ -37259,7 +37257,7 @@
         <v>45488</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>145069</v>
       </c>
@@ -37279,7 +37277,7 @@
         <v>45958</v>
       </c>
     </row>
-    <row r="559" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>145069</v>
       </c>
@@ -37299,7 +37297,7 @@
         <v>45939</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>145070</v>
       </c>
@@ -37319,7 +37317,7 @@
         <v>45958</v>
       </c>
     </row>
-    <row r="561" spans="1:6" ht="50" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:6" ht="50" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>145070</v>
       </c>
@@ -37339,7 +37337,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="562" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>145070</v>
       </c>
@@ -37359,7 +37357,7 @@
         <v>45958</v>
       </c>
     </row>
-    <row r="563" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>145070</v>
       </c>
@@ -37379,7 +37377,7 @@
         <v>45957</v>
       </c>
     </row>
-    <row r="564" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:6" ht="25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>145070</v>
       </c>
@@ -37400,7 +37398,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F564" xr:uid="{2C6ABB9E-6A8B-E24D-88D0-7BE911A40F07}"/>
+  <autoFilter ref="A1:F564" xr:uid="{2C6ABB9E-6A8B-E24D-88D0-7BE911A40F07}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="104784"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -37550,7 +37554,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>106077</v>
       </c>
@@ -37880,7 +37884,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" ht="62.5" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>104783</v>
       </c>
